--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N5_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.29285391206322</v>
+        <v>10.61008876071027</v>
       </c>
       <c r="D2" t="n">
-        <v>65.95387827406475</v>
+        <v>10.71750521953552</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
